--- a/Result/checksun_type/流行音樂及文化內容產業.xlsx
+++ b/Result/checksun_type/流行音樂及文化內容產業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>95.02000000000001</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>95.28</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>96.26</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>95.28</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>96.26000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>5858.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4471.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4471.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5862.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7957.5</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>7957.5</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-762.703227585248</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>5858</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>5858.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>94.78</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>95.22</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>96.35</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>96.34999999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2316.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4883.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4883.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>6311.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7982.72</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7982.72</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-898.1634135532122</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2316</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2316.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>94.5</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>95.14</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>96.44</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>95.14</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>96.44</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>5226.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>6079.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>6079.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>7106.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>8138.98</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>8138.98</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-680.1007001662601</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>5226</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>5226.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>94.5</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>95.08</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>96.54</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>95.08</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>96.54000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>5251.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>6168.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>6168</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>7168.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>8117.54</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>8117.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-656.0789417503911</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>5251</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>5251.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>94.96</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>95.1</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>96.67</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>96.67</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>3705.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>5965.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>5965</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>7215.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>8102.32</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>8102.32</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-601.0093246652077</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>3705</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>3705.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>95.46</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>95.1</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>96.79</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>96.79000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>7920.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>7253.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>7253.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>7494.4</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>8198.6</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>8198.6</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-335.2309672340452</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>7920</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>7920.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>96.14</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>95.14</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>96.94</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>95.14</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>96.94</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>8297.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7740.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7740.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>7531.4</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>8176.92</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>8176.92</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-395.1822077883107</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>8297</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>8297.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>96.5</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>95.18</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>97.07</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>95.18000000000001</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>97.06999999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>5667.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>8133.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>8133.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>8641.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>8081.88</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>8081.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-507.1060440162501</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>5667</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>5667.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>96.4</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>95.14</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>97.15</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>95.14</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>97.15000000000001</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>4236.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>8168.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>8168</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>8980.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>8209.38</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>8209.379999999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-367.1005941984413</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>4236</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>4236.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>96.03999999999999</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>94.97</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>97.22</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>97.22</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>10146.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>8465.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>8465</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>9210.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>8212.94</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>8212.940000000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-0.6606446659116045</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>10146</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>10146.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>95.7</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>94.78</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>97.29</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>94.78</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>97.29000000000001</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>10355.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>7735.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>7735.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>9187.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>8114.04</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>8114.04</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-110.3656937385167</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>10355</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>10355.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>57.76000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>57.54</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>54.47</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>54.47</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>58.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>252.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>252.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-82.85489821189958</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>58</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>58.1</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>54.4</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>132.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>299.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>299.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-69.69525090339852</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>132</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>58.58000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>54.37</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>54.37</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>403.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>0</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-56.33521007327556</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>403</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>403.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>58.5</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>57.22</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>54.29</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>54.29</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>552.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>0</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-64.27317995619728</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>552</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>552.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>57.98</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>54.19</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>54.19</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>118.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>0</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>0</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-89.28195193336404</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>118</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>57.38</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>56.54</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>54.08</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>56.54</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>54.08</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>291.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>0</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-75.32012790312513</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>291</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>291.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>56.62</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>56.22</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>53.98</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>0</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-66.91975283082633</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>0</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>56.58000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>55.91</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>53.9</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>175.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>0</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-66.91975283082633</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>175</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>56.64</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>55.57</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>53.79</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>55.57</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>53.79</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>0</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-33.36868258238928</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>0</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>57.14</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>55.35</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>53.7</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>62.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>396.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>396.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>929.9</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>398.84</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>398.84</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-33.36868258238928</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>62</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>57.94</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>55.12</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>53.67</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>53.67</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>354.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>562.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>562</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>950.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>404.02</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>404.02</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>15.88228378974236</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>354</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>354.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>88.47999999999999</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>83.56</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>83.29</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>83.29000000000001</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>58702801.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>40221683.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>40221683.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>43461987.8</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>22012771.5</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>22012771.5</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>4964149.079171807</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>58702801</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>58702801.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>88.36</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>83.16</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>83.28</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>83.16</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>83.28</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>58419358.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>31848485.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>31848485.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>39748956.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>22543702.08</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>22543702.08</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>3875376.410340749</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>58419358</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>58419358.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>87.56</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>82.6</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>83.26</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>83.26000000000001</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>39133272.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>27770887.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>27770887.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>38460489.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>22045319.38</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>22045319.38</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>2211949.47592707</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>39133272</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>39133272.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>87.24000000000001</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>82.14</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>83.23</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>82.14</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>83.23</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>18205955.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>35904398.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>35904398.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>35499616.4</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>21582978.9</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>21582978.9</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>1822993.445481565</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>18205955</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>18205955.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>87.04</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>81.85</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>83.25</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>81.84999999999999</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>83.25</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>26647033.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>50191372.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>50191372.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>34370422.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>21481272.04</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>21481272.04</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>3444447.600363646</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>26647033</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>26647033.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>86.18</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>81.57</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>83.26</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>81.56999999999999</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>83.26000000000001</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>16836808.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>46702291.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>46702291.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>32237015.5</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>21455371.18</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>21455371.18</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>4733393.478753638</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>16836808</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>16836808.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>85.52000000000001</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>83.28</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>83.28</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>38031368.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>47649428.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>47649428.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>32393860.2</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>21445022.68</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>21445022.68</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>7456790.502212424</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>38031368</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>38031368.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>84.6</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>81.08</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>81.08</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>83.3</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>79800829.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>49150091.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>49150091.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>29506950.3</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>20817010.4</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>20817010.4</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>8810198.017788813</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>79800829</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>79800829.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>82.84</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>80.78</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>83.28</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>83.28</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>89640824.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>35094834.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>35094834.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>23143841.1</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>19796469.42</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>19796469.42</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>5953688.003691196</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>89640824</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>89640824.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>81.25999999999999</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>80.53</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>83.31</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>80.53</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>83.31</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>9201630.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>18549473.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>18549473.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>15637481.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>18480153.54</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>18480153.54</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>606042.5191342011</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>9201630</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>9201630.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>80.47999999999999</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>80.44</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>83.4</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>80.44</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>83.40000000000001</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>21572491.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>17771739.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>17771739.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>17837408.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>18693805.14</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>18693805.14</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>1563389.665512271</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>21572491</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>21572491.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>140.8</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>146.85</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>150.36</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>146.85</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>150.36</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>40195.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>52569.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>52569</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>63826.3</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>114514.58</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>114514.58</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-25204.40341820469</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>40195</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>40195.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>139.9</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>147.72</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>150.67</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>147.72</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>150.67</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>33617.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>59107.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>59107.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>71872.6</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>118093.0</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>118093</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-25155.01131175055</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>33617</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>33617.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>138.6</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>148.68</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>151.13</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>148.68</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>151.13</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>72467.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>64386.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>64386.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>83398.7</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>121719.32</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>121719.32</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-23481.27218425355</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>72467</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>72467.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>138.0</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>149.4</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>151.5</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>151.5</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>62948.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>63654.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>63654</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>104111.4</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>122395.14</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>122395.14</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-24414.09942410591</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>62948</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>62948.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>138.1</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>150.32</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>151.94</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>150.32</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>151.94</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>53618.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>69291.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>69291.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>119014.3</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>123514.58</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>123514.58</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-23854.88478731981</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>53618</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>53618.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>137.3</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>150.82</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>152.34</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>150.82</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>152.34</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>72887.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>75083.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>75083.60000000001</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>160739.1</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>132563.58</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>132563.58</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-21204.40370664967</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>72887</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>72887.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>137.3</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>151.4</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>152.77</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>151.4</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>152.77</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>60011.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>84637.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>84637.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>213495.1</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>135994.8</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>135994.8</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-18725.23774474053</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>60011</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>60011.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>137.5</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>152.07</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>153.32</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>152.07</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>153.32</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>68806.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>102411.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>102411.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>235568.5</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>138161.06</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>138161.06</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-13135.24216541534</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>68806</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>68806.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>137.3</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>152.65</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>153.79</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>152.65</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>153.79</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>91134.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>144568.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>144568.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>266581.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>149561.5</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>149561.5</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-5622.739831900253</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>91134</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>91134.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>138.7</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>153.35</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>154.6</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>153.35</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>154.6</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>82580.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>168737.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>168737.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>269466.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>154939.62</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>154939.62</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>2917.932781403506</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>82580</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>82580.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>141.5</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>154.05</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>155.28</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>154.05</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>155.28</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>120658.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>246394.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>246394.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>269572.9</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>158308.66</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>158308.66</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>15931.18177250159</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>120658</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>120658.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>37.43</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>37.74</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>37.44</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>37.74</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>37.44</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>187.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>1805.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>1805.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>1872.0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>3131.08</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>3131.08</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-236.052413060745</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>187</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>187.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>37.54</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>37.8</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>37.43</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>37.43</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>2935.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>2464.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>2464.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>2448.1</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>3182.04</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>3182.04</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-76.53727705964411</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>2935</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>2935.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>37.64</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>37.42</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>37.42</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>2820.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>2348.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>2348</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>2643.4</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>3215.8</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>3215.8</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-140.3536085916548</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>2820</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>2820.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>37.73</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>37.91</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>37.42</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>37.42</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>1729.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>2063.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>2063.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>2582.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>3245.92</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>3245.92</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-214.1857390448249</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>1729</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>1729.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>37.77999999999999</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>37.94</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>37.4</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>1357.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>1952.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>1952.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>2565.6</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>3334.42</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>3334.42</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-195.1178632977535</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>1357</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>1357.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,21 +22127,17 @@
           <t>37.81</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>37.95</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
+      <c r="AM51" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>37.36</v>
+      </c>
+      <c r="AO51" t="inlineStr">
         <is>
           <t>37.36</t>
         </is>
       </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>37.36</t>
-        </is>
-      </c>
       <c r="AP51" t="inlineStr">
         <is>
           <t>-42.08</t>
@@ -22476,20 +22178,16 @@
           <t>3483.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>1938.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>1938.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>2578.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>3357.86</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>3357.86</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-121.052402827017</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>3483</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>3483.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>37.83</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>37.95</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>37.32</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>37.32</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>2351.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>2431.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>2431.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>2329.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>3333.96</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>3333.96</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-238.7070163392859</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>2351</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>2351.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>37.79</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>37.97</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>37.28</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>37.28</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>1397.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>2938.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>2938.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>2223.5</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>3309.96</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>3309.96</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-276.9740707732667</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>1397</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>1397.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>37.70999999999999</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>37.98</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>37.24</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>37.24</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>1175.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>3102.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>3102.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>2213.6</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>3370.08</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>3370.08</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-219.5350745799087</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>1175</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>1175.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>37.66</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>37.95</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>37.2</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>1286.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>3178.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>3178.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>2260.7</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>3407.36</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>3407.36</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-105.8531130686861</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>1286</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>1286.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>37.64</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>37.17</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>37.17</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>5948.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>3219.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>3219.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>2369.5</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>3514.32</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>3514.32</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>48.43730027122774</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>5948</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>5948.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>48.32</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>49.46</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>55.04</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>55.04</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>289324693.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>359053739.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>359053739.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>779219302.6</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1233289107.3</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1233289107.3</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-90860825.19125909</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>289324693</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>289324693.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>48.31</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>49.57</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>55.39</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>55.39</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>298587633.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>427404646.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>427404646.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>788465115.2</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>1336844077.5</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>1336844077.5</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-80434512.81531477</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>298587633</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>298587633.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>48.41</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>49.77</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>55.78</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>55.78</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>302147334.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>549695262.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>549695262.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>789932410.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>1388106125.2</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>1388106125.2</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-63659577.53484738</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>302147334</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>302147334.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>49.14</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>56.17</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>56.17</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>429086972.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>664802561.8</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>664802561.8</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>805598718.5</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>1482928219.1</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>1482928219.1</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-37803224.47222078</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>429086972</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>429086972.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>49.73999999999999</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>50.18</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>56.62</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>56.62</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>476122067.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>751503060.6</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>751503060.6</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>853426202.9</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>1565117969.24</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>1565117969.24</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-13116137.5801748</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>476122067</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>476122067.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>50.16</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>50.38</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>57.1</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>631079227.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>1199384865.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>1199384865.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>852262787.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>1647059956.98</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>1647059956.98</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>17580088.42918277</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>631079227</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>631079227.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>50.69</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>50.56</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>57.56</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>910040711.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>1149525583.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>1149525583.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>840320195.5</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>1776903570.96</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>1776903570.96</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>44201426.71293712</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>910040711</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>910040711.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>50.32</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>50.72</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>58.07</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>58.07</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>877683832.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>1030169557.8</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>1030169557.8</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>806899222.5</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>1957468999.34</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>1957468999.34</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>50764557.16426682</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>877683832</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>877683832.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>49.52</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>50.73</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>58.46</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>862589466.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>946394875.2</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>946394875.2</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>771003853.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2163437979.1</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2163437979.1</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>61794246.37458563</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>862589466</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>862589466.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>48.86</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>50.84</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>58.9</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>2715531091.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>955349345.2</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>955349345.2</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>721647627.7</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2402549153.18</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2402549153.18</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>76961261.37594843</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>2715531091</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>2715531091.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>48.84</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>50.98</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>59.29</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>59.29</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>381782819.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>505140710.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>505140710.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>501963719.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2548936714.28</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2548936714.28</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-102649650.6355312</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>381782819</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>381782819.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
